--- a/public/crawlability-manpowergroup-september-2026.xlsx
+++ b/public/crawlability-manpowergroup-september-2026.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של manpowergroup ב-SE Ranking (הסריקה האחרונה: 2024-09-01).</t>
+          <t>להריץ מחדש את ה-Website Audit של manpowergroup ב-SE Ranking (הסריקה האחרונה: 2024-09-01); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (307) של HubSpot בגלל הפרמטר hsLang בקישורים הפנימיים. לעדכן את הקישורים לכתובת ללא הפרמטר.</t>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). הפניה זמנית (307) של HubSpot בגלל הפרמטר hsLang בקישורים הפנימיים. לעדכן את הקישורים לכתובת ללא הפרמטר.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">

--- a/public/crawlability-manpowergroup-september-2026.xlsx
+++ b/public/crawlability-manpowergroup-september-2026.xlsx
@@ -509,14 +509,14 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>הפניות זמניות (302/307): 14 כתובות (הבולטת: https://manpowergroup.co.il/contacts?hsLang=he, 33 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>להוסיף שורת Sitemap עם כתובת מפת האתר לקובץ robots.txt.</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>להוסיף שורת Sitemap עם כתובת מפת האתר לקובץ robots.txt.</t>
+          <t>quest.manpowergroup.co.il: להגדיר noindex (כתובת אחת באינדקס).</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>quest.manpowergroup.co.il: להגדיר noindex (כתובת אחת באינדקס).</t>
+          <t>הפניות זמניות (302/307): 13 כתובות (הבולטת: https://manpowergroup.co.il/contacts?hsLang=he, 33 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1515,53 +1515,6 @@
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>https://manpowergroup.co.il/cookies-policy?hsLang=he</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>307</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>307 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>https://manpowergroup.co.il/cookies-policy</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>הפניות זמניות (302/307)</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). הפניה זמנית (307) של HubSpot בגלל הפרמטר hsLang בקישורים הפנימיים. לעדכן את הקישורים לכתובת ללא הפרמטר.</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>https://manpowergroup.co.il/cookies-policy</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>

--- a/public/crawlability-manpowergroup-september-2026.xlsx
+++ b/public/crawlability-manpowergroup-september-2026.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום פעולות" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לולאות, שרשראות, 302" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ללא טיפול" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +502,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: 2 כתובות (הבולטת: https://www.manpowergroup.co.il/?hsLang=he, 16 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>שרשראות הפניות: 2 כתובות; הבולטת https://www.manpowergroup.co.il/?hsLang=he (16 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -546,7 +547,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>הפניות זמניות (302/307): 13 כתובות (הבולטת: https://manpowergroup.co.il/contacts?hsLang=he, 33 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>הפניות זמניות (302/307): 13 כתובות; הבולטת https://manpowergroup.co.il/contacts?hsLang=he (33 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -561,7 +562,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של manpowergroup ב-SE Ranking (הסריקה האחרונה: 2024-09-01); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של manpowergroup ב-SE Ranking; הסריקה האחרונה: 2024-09-01.</t>
         </is>
       </c>
     </row>
@@ -1531,6 +1532,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>כתובת</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>קוד בסריקה 23.09</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>קוד בבדיקה חיה 27.09</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>יעד סופי / יעד להפניה</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>קפיצות</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>קישורים נכנסים</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>עמודי מקור (עד 10)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>סוג</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>פעולה נדרשת</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>יעד מומלץ להפניית 301</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>עדיפות</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>https://manpowergroup.co.il/cookies-policy?hsLang=he</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>307 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>https://manpowergroup.co.il/cookies-policy</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>https://manpowergroup.co.il/cookies-policy</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1825,7 +1957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1979,7 +2111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/public/crawlability-manpowergroup-september-2026.xlsx
+++ b/public/crawlability-manpowergroup-september-2026.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -532,37 +532,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>quest.manpowergroup.co.il: להגדיר noindex (כתובת אחת באינדקס).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
           <t>הפניות זמניות (302/307): 13 כתובות; הבולטת https://manpowergroup.co.il/contacts?hsLang=he (33 קישורים נכנסים).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של manpowergroup ב-SE Ranking; הסריקה האחרונה: 2024-09-01.</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2027,7 +1997,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>quest.manpowergroup.co.il</t>
+          <t>talentsolutions.manpowergroup.co.il</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2037,70 +2007,31 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>מערכת שאלונים - דף כניסה</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Talent Solutions | פתרונות חכמים לניהול, גיוס ופיתוח טאלנטים</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>index, follow, max-image-preview:large, max-snippet:-1, max-video-preview:-1</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>https://talentsolutions.manpowergroup.co.il/</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>מערכת שאלונים</t>
+          <t>אתר נפרד (פרויקט ב-SE Ranking)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>להגדיר noindex (כתובת אחת באינדקס).</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>talentsolutions.manpowergroup.co.il</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Talent Solutions | פתרונות חכמים לניהול, גיוס ופיתוח טאלנטים</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>index, follow, max-image-preview:large, max-snippet:-1, max-video-preview:-1</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>https://talentsolutions.manpowergroup.co.il/</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>אתר נפרד (פרויקט ב-SE Ranking)</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
           <t>ללא פעולה.</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
